--- a/examples/advanced_template.xlsx
+++ b/examples/advanced_template.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0원"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,13 +33,26 @@
       <sz val="16"/>
     </font>
     <font>
+      <color rgb="00FF6600"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="00CCCCCC"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="5">
@@ -84,22 +97,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,14 +482,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,19 +520,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{# 아래부터 부서별 직원 목록 #}</t>
+          <t>부제: {{ subtitle|default('부제 없음') }}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>{# 아래부터 부서별 직원 목록 - 새 기능 테스트 포함 #}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>{% for dept in departments %}</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -521,20 +547,41 @@
               <color rgb="002E75B6"/>
               <sz val="14"/>
             </rPr>
-            <t>📁 {{ dept.name }}</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+            <t>📁 {{ loop.index }}. {{ dept.name }}</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{% if loop.first %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>⭐ 첫 번째 부서입니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{% endif %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{% if dept.description %}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">설명: </t>
@@ -549,44 +596,87 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{% endif %}</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>직원 수: {{ dept.employees|length }}명</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{% if dept.is_active and dept.employees %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>✅ 활성 부서 (직원 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{% endif %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>직책</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>급여</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{% for emp in dept.employees %}</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>{{ loop.index }}</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -599,31 +689,36 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>{{ emp.position }}</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>{{ emp.salary }}</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>{{ emp.status }}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>{{ '✅ 재직' if emp.status == '재직' else '⏸️ 휴직' }}</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>{{ '🌟 고급' if emp.position in senior_positions else '' }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>{% endfor %}</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">총 </t>
@@ -633,7 +728,7 @@
               <b val="1"/>
               <color rgb="00C65911"/>
             </rPr>
-            <t>{{ dept.employee_count }}</t>
+            <t>{{ dept.employees|length }}</t>
           </r>
           <r>
             <t xml:space="preserve">명, 평균 급여: </t>
@@ -643,29 +738,54 @@
               <b val="1"/>
               <color rgb="002E75B6"/>
             </rPr>
-            <t>{{ dept.avg_salary }}</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+            <t>{{ dept.avg_salary|default('계산 중') }}</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{% if not loop.last %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>{% endif %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>{% endfor %}</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8">
+    <row r="26">
+      <c r="A26" s="11">
         <f>== 전체 요약 ===</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>부서 목록: {{ department_names|join(', ') }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">전체 직원: </t>
@@ -679,8 +799,39 @@
             <t>{{ total_employees }}</t>
           </r>
           <r>
-            <t>명</t>
-          </r>
+            <t xml:space="preserve">명 (총 </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002E75B6"/>
+            </rPr>
+            <t>{{ departments|length }}</t>
+          </r>
+          <r>
+            <t>개 부서)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{% if show_footer or debug_mode %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>📋 이 리포트는 자동 생성되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{% endif %}</t>
         </is>
       </c>
     </row>

--- a/examples/advanced_template.xlsx
+++ b/examples/advanced_template.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -835,6 +835,96 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="11">
+        <f>== 새 필터 테스트 ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>upper: {{ test_name|upper }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lower: {{ test_name|lower }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>title: {{ test_title_text|title }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>trim: [{{ test_spaces|trim }}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>replace: {{ test_replace|replace('world', 'Korea') }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>round: {{ test_float|round(2) }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>abs: {{ test_negative|abs }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>int: {{ test_float|int }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>float: {{ test_int_str|float }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>first: {{ test_list|first }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>last: {{ test_list|last }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>chained: {{ test_spaces|trim|upper }}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
